--- a/src/test_inventory_data.xlsx
+++ b/src/test_inventory_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,31 @@
           <t>Unit Volume (L)</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>UOM</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cost Price</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MOQ</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Lead Time (Days)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Daily Usage</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,93 +530,148 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PKG-BOX-3030</t>
+          <t>RAW-SUG-BRN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cardboard Box 30x30</t>
+          <t>Brown Sugar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Box Expert Ent</t>
+          <t>Gula Prai Sdn Bhd</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PKG</t>
+          <t>RAW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Ingredient</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>25</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FG-VAN-750</t>
+          <t>RAW-GLU-SYR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vanilla Syrup 750ml</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Glucose Syrup</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ChemSource Inc</t>
+        </is>
+      </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>800</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FG</t>
+          <t>RAW</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finished Product</t>
+          <t>Ingredient</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.2</v>
+        <v>25</v>
       </c>
       <c r="H4" t="n">
-        <v>0.75</v>
+        <v>20</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>200</v>
+      </c>
+      <c r="L4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RAW-RIC-10</t>
+          <t>RAW-WAT-FIL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rice 10kg Pack</t>
+          <t>Filtered Water (Industrial)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bernas</t>
+          <t>Utility Provider</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>10000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -600,50 +680,2389 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dry Goods</t>
+          <t>Liquid</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEW-ITEM-X</t>
+          <t>RAW-VAN-EXT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unknown New Item</t>
+          <t>Vanilla Extract Premium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mystery Supply Co.</t>
+          <t>Flavor House Ltd</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>150</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Flavoring</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>120</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RAW-HAZ-EXT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hazelnut Extract</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Flavor House Ltd</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>80</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flavoring</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>145</v>
+      </c>
+      <c r="K7" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="L7" t="n">
+        <v>30</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RAW-CAR-FLV</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Caramel Flavoring</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Flavor House Ltd</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>95</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>RAW</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Flavoring</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>110</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RAW-COC-POW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cocoa Powder (Dutch Process)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Barry Callebaut</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>600</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ingredient</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>35</v>
+      </c>
+      <c r="K9" t="n">
+        <v>100</v>
+      </c>
+      <c r="L9" t="n">
+        <v>45</v>
+      </c>
+      <c r="M9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RAW-MLK-POW</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Skimmed Milk Powder</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dairy Suppliers Co</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>400</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ingredient</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>28</v>
+      </c>
+      <c r="K10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L10" t="n">
+        <v>21</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RAW-COF-ARA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Arabica Coffee Beans</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bean Importers</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bean</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>45</v>
+      </c>
+      <c r="K11" t="n">
+        <v>300</v>
+      </c>
+      <c r="L11" t="n">
+        <v>60</v>
+      </c>
+      <c r="M11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RAW-COF-ROB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Robusta Coffee Beans</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bean Importers</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bean</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K12" t="n">
+        <v>300</v>
+      </c>
+      <c r="L12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RAW-TEA-BLK</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Black Tea Dust</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tea Garden Cameron</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>800</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>18</v>
+      </c>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14</v>
+      </c>
+      <c r="M13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RAW-TEA-GRN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Green Tea Matcha</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kyoto Import</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>250</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" t="n">
+        <v>60</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RAW-PRE-BEN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sodium Benzoate</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ChemSource Inc</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Additive</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>15</v>
+      </c>
+      <c r="K15" t="n">
+        <v>25</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RAW-ACD-CIT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Citric Acid Anhydrous</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ChemSource Inc</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>250</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Additive</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>25</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>50</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RAW-COL-RED</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Food Coloring E129 (Red)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Colorant Co</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Additive</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>85</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>21</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RAW-COL-BLU</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Food Coloring E133 (Blue)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Colorant Co</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Additive</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>90</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RAW-SAL-SEA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sea Salt (Fine)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Salt Supplier</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>300</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ingredient</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>50</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
+      <c r="L19" t="n">
+        <v>7</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RAW-EMU-LEC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Soy Lecithin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ChemSource Inc</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>120</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Additive</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="n">
+        <v>20</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>22</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20</v>
+      </c>
+      <c r="L20" t="n">
+        <v>21</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RAW-SPI-CIN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cinnamon Powder</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Spices &amp; Co</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spice</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>65</v>
+      </c>
+      <c r="K21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" t="n">
+        <v>14</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PKG-BTL-GLS-750</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Glass Bottle 750ml (Clear)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Glass Works Ltd</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PKG</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>45</v>
+      </c>
+      <c r="M22" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PKG-BTL-PET-1L</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PET Bottle 1L (Round)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Plastic Tech</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PKG</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>21</v>
+      </c>
+      <c r="M23" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PKG-CAP-BLK</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Screw Cap 28mm (Black)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Plastic Tech</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PKG</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Closure</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>21</v>
+      </c>
+      <c r="M24" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PKG-CAP-WHT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Screw Cap 28mm (White)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Plastic Tech</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PKG</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Closure</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L25" t="n">
+        <v>21</v>
+      </c>
+      <c r="M25" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PKG-LAB-VAN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Label - Vanilla Syrup</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Print Press</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PKG</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L26" t="n">
+        <v>14</v>
+      </c>
+      <c r="M26" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PKG-LAB-HAZ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Label - Hazelnut Syrup</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Print Press</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PKG</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>14</v>
+      </c>
+      <c r="M27" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PKG-LAB-GEN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Label - Generic Back</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Print Press</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PKG</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>14</v>
+      </c>
+      <c r="M28" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PKG-BOX-6X750</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Carton Box (6 x 750ml)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Box Expert Ent</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PKG</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Carton</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>500</v>
+      </c>
+      <c r="L29" t="n">
+        <v>14</v>
+      </c>
+      <c r="M29" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PKG-SHR-WRP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Shrink Wrap Roll (Heavy)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Plastic Tech</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>50</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PKG</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ROLL</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>45</v>
+      </c>
+      <c r="K30" t="n">
+        <v>10</v>
+      </c>
+      <c r="L30" t="n">
+        <v>7</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PKG-PAL-WOO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Wooden Pallet (Standard)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Warehouse Supply</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>40</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PKG</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>15</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>80</v>
+      </c>
+      <c r="K31" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FG-SYR-VAN</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Vanilla Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>240</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FG-SYR-HAZ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Hazelnut Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>180</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>9</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FG-SYR-CAR</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Caramel Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>200</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FG-SAU-COC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Chocolate Sauce 1L</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>150</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sauces</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>15</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FG-SAU-CAR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Caramel Sauce 1L</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>120</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sauces</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FG-SYR-STR</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Strawberry Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>90</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FG-SYR-PEA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Peach Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>85</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FG-PUR-MAN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Mango Puree 1L</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>60</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Puree</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>18</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FG-SYR-BLU</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Blue Curacao Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>10</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FG-SYR-PEP</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Peppermint Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>50</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FG-SYR-COC</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Coconut Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>70</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FG-SYR-ALM</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Almond Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>45</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>11</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FG-SYR-IRI</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Irish Cream Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>110</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FG-SYR-SLC</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Salted Caramel Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>130</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FG-SYR-RAS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Raspberry Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>40</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>FG-CON-LEM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Lemon Tea Concentrate 1L</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>300</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Concentrate</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>12</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>FG-CON-GRN</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Green Tea Concentrate 1L</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>250</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Concentrate</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FG-BAS-COF</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Coffee Base Concentrate</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>500</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>20</v>
+      </c>
+      <c r="H49" t="n">
+        <v>20</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>DRUM</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>180</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>FG-SYR-TOF</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Toffee Nut Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>95</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FG-SYR-ROS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Rose Syrup 750ml</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>80</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Syrups</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
